--- a/nr-update-idnatstruct-descr/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-update-idnatstruct-descr/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T15:39:50+00:00</t>
+    <t>2025-02-04T15:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,7 +947,7 @@
     <t>Organization.identifier:idNatSt.value</t>
   </si>
   <si>
-    <t>Identifiant national de la structure</t>
+    <t>Identifiant national de la structure. Cet identifiant ne doit pas être construit ni interprété, la donnée peut être trouvée dans l'annuaire santé.</t>
   </si>
   <si>
     <t>L'idNatStruct est construit, selon le cas, de cette manière : 0 + ADELI rang, 1 + Numéro FINESS Etablissement, 2 + Numéro SIREN, 3 + Numéro SIRET, 4 + RPPS rang ou identifiant technique de la structure</t>
